--- a/output/pdf_financials_xlsx/PET.xlsx
+++ b/output/pdf_financials_xlsx/PET.xlsx
@@ -2164,16 +2164,16 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>0</v>
+        <v>-0.159</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>-0.141</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>-0.141</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>-0.141</v>
       </c>
     </row>
     <row r="92">
@@ -4176,7 +4176,11 @@
           <t>Currency translation reserve</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
         <v>-0.159</v>
       </c>
@@ -7534,7 +7538,11 @@
           <t>Currency translation reserve (159)</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E123" s="5" t="n">
         <v>-0.179</v>
       </c>

--- a/output/pdf_financials_xlsx/PET.xlsx
+++ b/output/pdf_financials_xlsx/PET.xlsx
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>63.034</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>28.444</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>35.141</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>35.721</v>
       </c>
     </row>
     <row r="35">
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>63.034</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>28.444</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>35.141</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>35.721</v>
       </c>
     </row>
     <row r="37">
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>233.533</v>
+        <v>170.499</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>210.26</v>
+        <v>181.816</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>86.97</v>
+        <v>51.829</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>92.179</v>
+        <v>56.458</v>
       </c>
     </row>
     <row r="49">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">

--- a/output/pdf_financials_xlsx/PET.xlsx
+++ b/output/pdf_financials_xlsx/PET.xlsx
@@ -2551,16 +2551,16 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>3.643</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>6.579</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>8.178000000000001</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="113">
@@ -8802,7 +8802,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E159" s="5" t="n">
         <v>3.643</v>
       </c>
@@ -12064,7 +12068,11 @@
           <t>Proceeds on disposal of property and equipment 3,643</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E251" s="5" t="n">
         <v>5.167</v>
       </c>

--- a/output/pdf_financials_xlsx/PET.xlsx
+++ b/output/pdf_financials_xlsx/PET.xlsx
@@ -1774,7 +1774,7 @@
         <v>76.881</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>77.126</v>
       </c>
     </row>
     <row r="71">
@@ -1793,7 +1793,7 @@
         <v>76.881</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>77.126</v>
       </c>
     </row>
     <row r="72">
@@ -1869,7 +1869,7 @@
         <v>1.782</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>85.727</v>
+        <v>8.601000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -1964,7 +1964,7 @@
         <v>3.706576569990287</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>2.940625190793089</v>
+        <v>3.725430937989702</v>
       </c>
     </row>
     <row r="81">
@@ -2456,16 +2456,16 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>0</v>
+        <v>6.248</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>5.855</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>7.203</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>6.015</v>
       </c>
     </row>
     <row r="108">
@@ -2627,16 +2627,16 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-3.424</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-3.257</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-2.121</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-2.188</v>
       </c>
     </row>
     <row r="117">
@@ -3712,7 +3712,11 @@
           <t>Lease liabilities 7</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -8002,7 +8006,11 @@
           <t>Share-based compensation expense 20</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -8768,7 +8776,11 @@
           <t>Purchases of intangible assets 9</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -9414,7 +9426,11 @@
           <t>Share-based compensation expense 18</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -10018,7 +10034,11 @@
           <t>Purchase of intangible assets 8</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E194" s="5" t="n">
         <v>-3.424</v>
       </c>
@@ -10292,7 +10312,11 @@
           <t>Share-based compensation expense 19</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E202" s="5" t="n">
         <v>6.248</v>
       </c>
@@ -11012,7 +11036,11 @@
           <t>Share-based compensation expense 19 6,248</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E222" s="5" t="n">
         <v>2.199</v>
       </c>
